--- a/WD template.xlsx
+++ b/WD template.xlsx
@@ -1,137 +1,198 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Phil\dev\convest\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{934E7449-1E8A-419E-B078-814A5263CCCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{47FD1F4C-FF32-456B-BC7D-4B7F5AC91AFA}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
+  <si>
+    <t>Works Package Name</t>
+  </si>
+  <si>
+    <t>Description (Inclusions &amp; Exclusions)</t>
+  </si>
   <si>
     <t>Balustrading &amp; Metalwork</t>
   </si>
   <si>
+    <t>Includes balustrades, handrails, architectural metalwork, and secondary steelwork. Excludes primary structural steel.</t>
+  </si>
+  <si>
     <t>Curtain walling, Windows &amp; External Door</t>
   </si>
   <si>
+    <t>Includes external glazed facades, windows, and external doors. Excludes internal doors and internal glazed partitions.</t>
+  </si>
+  <si>
     <t>Demolition</t>
   </si>
   <si>
+    <t>Includes all site clearance, demolition, and removal of materials. Excludes groundworks excavation.</t>
+  </si>
+  <si>
     <t>Groundworks</t>
   </si>
   <si>
+    <t>Includes excavation, earthworks, foundations, and below-ground drainage. Excludes piling and structural frame.</t>
+  </si>
+  <si>
     <t>Highways</t>
   </si>
   <si>
+    <t>Includes public road construction, Section 278 works, and major paving. Excludes internal site landscaping.</t>
+  </si>
+  <si>
     <t>Lifts</t>
   </si>
   <si>
+    <t>Includes passenger and goods lifts, escalators, and moving walkways. Excludes lift shaft construction.</t>
+  </si>
+  <si>
     <t>Masonry</t>
   </si>
   <si>
+    <t>Includes brickwork, blockwork, damp proof courses, and wall ties. Excludes external stone cladding.</t>
+  </si>
+  <si>
     <t>Mechanical &amp; Electrical</t>
   </si>
   <si>
+    <t>Includes HVAC, plumbing, water supply, lighting, power, and fire alarms. Excludes external utilities infrastructure.</t>
+  </si>
+  <si>
     <t>Metal Doors</t>
   </si>
   <si>
+    <t>Includes steel doors, security doors, and louvres. Excludes timber doors and glazed doors.</t>
+  </si>
+  <si>
     <t>PCC Lift Shaft &amp; Stairs</t>
   </si>
   <si>
+    <t>Includes precast concrete stairs, landings, and lift shaft panels. Excludes in-situ concrete.</t>
+  </si>
+  <si>
     <t>Piling</t>
   </si>
   <si>
+    <t>Includes bored, driven, and CFA piling, and pile caps. Excludes general groundworks excavation.</t>
+  </si>
+  <si>
     <t>Roofing (Hotmelt)</t>
   </si>
   <si>
+    <t>Includes hot melt roofing systems, insulation, and roof coverings. Excludes structural roof decking.</t>
+  </si>
+  <si>
     <t>SFS</t>
   </si>
   <si>
+    <t>Includes Steel Framing Systems, infill framing, and external boarding. Excludes internal metal stud partitions.</t>
+  </si>
+  <si>
     <t>Siphonic Drainage</t>
   </si>
   <si>
+    <t>Includes siphonic roof drainage systems and associated pipework. Excludes below-ground drainage.</t>
+  </si>
+  <si>
     <t>Structural Steelwork</t>
   </si>
   <si>
+    <t>Includes primary steel frame, columns, and structural beams. Excludes secondary steel and SFS.</t>
+  </si>
+  <si>
     <t>Metal Decking</t>
   </si>
   <si>
+    <t>Includes profiled steel decking for composite floors. Excludes concrete topping.</t>
+  </si>
+  <si>
     <t>Raised Access Floors</t>
   </si>
   <si>
+    <t>Includes pedestals, floor panels, and stringers. Excludes floor finishes.</t>
+  </si>
+  <si>
     <t>Ceramic Tiling</t>
   </si>
   <si>
+    <t>Includes wall and floor tiling, grout, and adhesives. Excludes screeding.</t>
+  </si>
+  <si>
     <t>Cladding</t>
   </si>
   <si>
+    <t>Includes external rainscreen, panels, and weatherproofing. Excludes masonry facades.</t>
+  </si>
+  <si>
     <t>Joinery</t>
   </si>
   <si>
+    <t>Includes internal timber doors, skirting, architraves, and fitted furniture. Excludes structural timber.</t>
+  </si>
+  <si>
     <t>Painting and Decorating</t>
   </si>
   <si>
+    <t>Includes painting to walls, ceilings, and woodwork. Excludes specialist intumescent coatings.</t>
+  </si>
+  <si>
     <t>Road Markings</t>
   </si>
   <si>
+    <t>Includes line painting, symbols, and reflective studs on hardstandings. Excludes road surfacing.</t>
+  </si>
+  <si>
     <t>Screeding</t>
   </si>
   <si>
+    <t>Includes floor screeds, levelling compounds, and acoustic underlays. Excludes final floor finishes.</t>
+  </si>
+  <si>
     <t>Signage</t>
   </si>
   <si>
+    <t>Includes internal and external wayfinding, statutory, and architectural signage.</t>
+  </si>
+  <si>
     <t>Wall Protection Rails</t>
   </si>
   <si>
+    <t>Includes crash rails, corner guards, and handrails for wall protection.</t>
+  </si>
+  <si>
     <t>Scaffold/Hoist</t>
   </si>
   <si>
-    <t>Works Package Name</t>
+    <t>Includes temporary access scaffolding, hoists, and edge protection. Excludes permanent works.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -156,21 +217,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -217,7 +270,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -269,7 +322,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -330,309 +383,400 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE056E1E-BE7F-42A1-881D-F5FA1AABAEAB}">
-  <dimension ref="A1:A27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33" customWidth="true" style="0"/>
+    <col min="2" max="2" width="18.86328125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>